--- a/Result/profitability/1708.xlsx
+++ b/Result/profitability/1708.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.93</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9</v>
+        <v>0.8612500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>32.75875</v>
+        <v>31.90375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9012500000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N3" t="n">
-        <v>32.825</v>
+        <v>32.66625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9825</v>
+        <v>0.96125</v>
       </c>
       <c r="N4" t="n">
-        <v>34.235</v>
+        <v>34.03375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8625</v>
+        <v>0.9575000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>31.725</v>
+        <v>31.575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8850000000000001</v>
+        <v>0.85875</v>
       </c>
       <c r="N6" t="n">
-        <v>30.41</v>
+        <v>29.96625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8075000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1425</v>
+        <v>27.535</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7225</v>
+        <v>0.69125</v>
       </c>
       <c r="N8" t="n">
-        <v>26.33375</v>
+        <v>26.1375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4712499999999999</v>
+        <v>0.47125</v>
       </c>
       <c r="N12" t="n">
         <v>21.3125</v>
@@ -2026,7 +2026,7 @@
         <v>0.49</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5237499999999999</v>
+        <v>0.52375</v>
       </c>
       <c r="N13" t="n">
         <v>23.805</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E75" t="n">
+        <v>509</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>287</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>283</v>
+      </c>
+      <c r="K75" t="n">
+        <v>215</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8912500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.6125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2252252252252253</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05135754007196602</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.199999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03973509933774833</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
